--- a/data/synthetic/messy_foyle/bookings summer OLD do not use.xlsx
+++ b/data/synthetic/messy_foyle/bookings summer OLD do not use.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t xml:space="preserve">Request Received </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,12 +517,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>booking confirmed</t>
+          <t>BOOKING CONFIRMED</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t xml:space="preserve">Request Received </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>placement offer</t>
+          <t>PLACEMENT OFFER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>booking confirmed</t>
+          <t>Booking Confirmed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Placement Re-allocation</t>
+          <t xml:space="preserve">Booking Confirmed </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>chased 2x</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t xml:space="preserve">Request Received </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -733,17 +733,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>placement offer</t>
+          <t>Placement Offer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking Confirmed </t>
+          <t>booking confirmed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/data/synthetic/messy_foyle/bookings summer OLD do not use.xlsx
+++ b/data/synthetic/messy_foyle/bookings summer OLD do not use.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
